--- a/test/fixtures/xlsx/nullable-elements/nullable-elements.xlsx
+++ b/test/fixtures/xlsx/nullable-elements/nullable-elements.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="54">
   <si>
     <t xml:space="preserve">~~table:Listing~~</t>
   </si>
@@ -138,6 +138,42 @@
   </si>
   <si>
     <t xml:space="preserve">a;\-;c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~~table:Folded~~</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Numbered columns that fold into one array whose elements may be absent.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tag1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">element 1 - and the group's answer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tag2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">element 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tag3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">element 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c</t>
   </si>
 </sst>
 </file>
@@ -182,18 +218,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="B2:H13"/>
+  <dimension ref="B2:M13"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
       <c r="B2" t="s">
         <v>0</v>
       </c>
+      <c r="J2" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="3">
       <c r="B3" t="s">
         <v>1</v>
       </c>
+      <c r="J3" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="4">
       <c r="B4" t="s">
@@ -217,6 +259,18 @@
       <c r="H4" t="s">
         <v>22</v>
       </c>
+      <c r="J4" t="s">
+        <v>2</v>
+      </c>
+      <c r="K4" t="s">
+        <v>44</v>
+      </c>
+      <c r="L4" t="s">
+        <v>47</v>
+      </c>
+      <c r="M4" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="5">
       <c r="B5" t="s">
@@ -240,6 +294,18 @@
       <c r="H5" t="s">
         <v>23</v>
       </c>
+      <c r="J5" t="s">
+        <v>3</v>
+      </c>
+      <c r="K5" t="s">
+        <v>45</v>
+      </c>
+      <c r="L5" t="s">
+        <v>48</v>
+      </c>
+      <c r="M5" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="6">
       <c r="B6" t="s">
@@ -263,6 +329,18 @@
       <c r="H6" t="s">
         <v>24</v>
       </c>
+      <c r="J6" t="s">
+        <v>4</v>
+      </c>
+      <c r="K6" t="s">
+        <v>46</v>
+      </c>
+      <c r="L6" t="s">
+        <v>46</v>
+      </c>
+      <c r="M6" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="7">
       <c r="B7" t="s">
@@ -286,6 +364,18 @@
       <c r="H7" t="s">
         <v>5</v>
       </c>
+      <c r="J7" t="s">
+        <v>5</v>
+      </c>
+      <c r="K7" t="s">
+        <v>5</v>
+      </c>
+      <c r="L7" t="s">
+        <v>5</v>
+      </c>
+      <c r="M7" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="8">
       <c r="B8" t="s">
@@ -307,6 +397,18 @@
         <v>6</v>
       </c>
       <c r="H8" t="s">
+        <v>6</v>
+      </c>
+      <c r="J8" t="s">
+        <v>6</v>
+      </c>
+      <c r="K8" t="s">
+        <v>6</v>
+      </c>
+      <c r="L8" t="s">
+        <v>6</v>
+      </c>
+      <c r="M8" t="s">
         <v>6</v>
       </c>
     </row>
@@ -332,6 +434,18 @@
       <c r="H9" t="s">
         <v>28</v>
       </c>
+      <c r="J9" t="s">
+        <v>25</v>
+      </c>
+      <c r="K9" t="s">
+        <v>51</v>
+      </c>
+      <c r="L9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M9" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="10">
       <c r="B10" t="s">
@@ -355,6 +469,18 @@
       <c r="H10" t="s">
         <v>32</v>
       </c>
+      <c r="J10" t="s">
+        <v>29</v>
+      </c>
+      <c r="K10" t="s">
+        <v>51</v>
+      </c>
+      <c r="L10" t="s">
+        <v>35</v>
+      </c>
+      <c r="M10" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="11">
       <c r="B11" t="s">
@@ -378,6 +504,18 @@
       <c r="H11" t="s">
         <v>28</v>
       </c>
+      <c r="J11" t="s">
+        <v>33</v>
+      </c>
+      <c r="K11" t="s">
+        <v>35</v>
+      </c>
+      <c r="L11" t="s">
+        <v>52</v>
+      </c>
+      <c r="M11" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="12">
       <c r="B12" t="s">
@@ -400,6 +538,18 @@
       </c>
       <c r="H12" t="s">
         <v>38</v>
+      </c>
+      <c r="J12" t="s">
+        <v>36</v>
+      </c>
+      <c r="K12" t="s">
+        <v>51</v>
+      </c>
+      <c r="L12" t="s">
+        <v>5</v>
+      </c>
+      <c r="M12" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="13">
